--- a/Docs/ПМ02_Видеохостинг_Отчёт/Учебная практика №2.xlsx
+++ b/Docs/ПМ02_Видеохостинг_Отчёт/Учебная практика №2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
   <si>
     <t xml:space="preserve">Шаблон отчёта по разделу 3.3 учебной практики ПМ.02</t>
   </si>
@@ -244,6 +244,21 @@
   </si>
   <si>
     <t xml:space="preserve">Дифференцированный зачет</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подвести итоги практики, подтвердить сформированные компетенции</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подготовил итоговое портфолио и презентацию. Систематизировал материалы всех этапов (1–11). Подготовил демонстрацию рабочего прототипа (клиент-серверное приложение на C#/Avalonia + ASP.NET Core + PostgreSQL). Выполнил анализ предметной области, проектирование, реализацию модулей, отладку, инспекцию, тестирование.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnlyOffice Writer, Google Презентации, GitHub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Портфолио (DOCX, PDF), презентация (PPTX, PDF), исходный код (ссылка на репозиторий), обновлённый Excel-дневник</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Учебная практика выполнена в полном объёме, сформированы компетенции, проект готов к защите.</t>
   </si>
   <si>
     <t xml:space="preserve">Подсказка: в графе «Что я сделал(а)» лучше писать конкретные действия: «составил диаграмму вариантов использования», «выделил 6 сущностей», «разработал 15 тест-кейсов» и т.п.</t>
@@ -1341,18 +1356,28 @@
       <c r="B18" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
+      <c r="C18" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="G18" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H18" s="10"/>
+      <c r="H18" s="10" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
